--- a/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,118 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
+    <t>ARZATE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>LUCIANA</t>
   </si>
 </sst>
 </file>
@@ -594,16 +489,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.93000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -669,16 +567,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H5">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +635,7 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -803,7 +704,7 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -862,16 +763,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.93000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -937,16 +841,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H5">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +863,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,323 +895,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920197</v>
+        <v>22330051920343</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920198</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920199</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920201</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920280</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920204</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920206</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920290</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920209</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920210</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920212</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920213</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920215</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920259</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -82,10 +82,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>ARZATE</t>
   </si>
   <si>
-    <t>TORRES</t>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
   </si>
   <si>
     <t>LUCIANA</t>
@@ -863,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -895,16 +901,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920343</v>
+        <v>22330051920144</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -914,6 +920,29 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920343</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
@@ -492,7 +492,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -501,10 +501,10 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>82.93000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
         <v>7.5</v>
@@ -635,13 +635,13 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -775,10 +775,10 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>82.93000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
         <v>7.5</v>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
@@ -82,19 +82,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARZATE</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
     <t>MEZA</t>
   </si>
   <si>
+    <t>LUCIANA</t>
+  </si>
+  <si>
     <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
   </si>
 </sst>
 </file>
@@ -901,13 +901,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920144</v>
+        <v>22330051920343</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -919,18 +919,18 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920343</v>
+        <v>22330051920144</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -82,19 +82,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
   </si>
 </sst>
 </file>
@@ -638,16 +629,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -661,16 +655,19 @@
         <v>34</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>34</v>
       </c>
-      <c r="E3">
-        <v>34</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -684,16 +681,19 @@
         <v>32</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>32</v>
       </c>
-      <c r="E4">
-        <v>32</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -707,16 +707,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>92.31</v>
+      </c>
+      <c r="H5">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -781,7 +784,7 @@
         <v>83.33</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -807,7 +810,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -833,7 +836,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -850,16 +853,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>96.15000000000001</v>
+        <v>92.31</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,47 +904,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920343</v>
+        <v>20330051920259</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920144</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
@@ -922,7 +922,7 @@
         <v>14</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,12 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
   </si>
 </sst>
 </file>
@@ -810,7 +804,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -836,7 +830,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -853,16 +847,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>92.31</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -902,29 +896,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920259</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20222.xlsx
@@ -769,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
